--- a/artfynd/A 24618-2022 artfynd.xlsx
+++ b/artfynd/A 24618-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 24618-2022 artfynd.xlsx
+++ b/artfynd/A 24618-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,64 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3044694</v>
+        <v>108216914</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Torsängsviken, V om, Vrm</t>
+          <t>Tenngårdsholmern, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>418209.9355460294</v>
+        <v>418204</v>
       </c>
       <c r="R2" t="n">
-        <v>6574795.714252992</v>
+        <v>6574969</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,29 +750,29 @@
           <t>Hammarö</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>S-Ham-0031</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-07-26</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-07-26</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>I nyckelbiotop söder om kanalen Sättersviken - Torsängsviken</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,18 +784,250 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Limnisk strandvåtmark</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Åke Johansson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Åke Johansson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>101998828</v>
+      </c>
+      <c r="B3" t="n">
+        <v>61491</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>106670</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Svart skogssnigel</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Arion ater ater</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Barrskogen, Tenngårdsholmen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>418225</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6574775</v>
+      </c>
+      <c r="S3" t="n">
+        <v>39</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-06-30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-06-30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Carl A Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Carl A Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3044694</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Torsängsviken, V om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>418210</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6574796</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>S-Ham-0031</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2011-07-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2011-07-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Värmland Floraväktarna</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Erik Eriksson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>

--- a/artfynd/A 24618-2022 artfynd.xlsx
+++ b/artfynd/A 24618-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -801,6 +806,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108216914</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101998828</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1032,8 +1047,18 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3044694</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>